--- a/Production_Schedule.xlsx
+++ b/Production_Schedule.xlsx
@@ -1304,7 +1304,7 @@
     </row>
     <row r="8">
       <c r="A8">
-        <f>IFERROR(SORTBY(HSTACK(SEQUENCE(ROWS(FILTER('Master Schedule'!$A$6:$A$500,('Master Schedule'!$AG$6:$AG$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")))),FILTER('Master Schedule'!$A$6:$A$500,('Master Schedule'!$AG$6:$AG$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),FILTER('Master Schedule'!$B$6:$B$500,('Master Schedule'!$AG$6:$AG$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),FILTER('Master Schedule'!$C$6:$C$500,('Master Schedule'!$AG$6:$AG$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),FILTER('Master Schedule'!$E$6:$E$500,('Master Schedule'!$AG$6:$AG$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),FILTER('Master Schedule'!$F$6:$F$500,('Master Schedule'!$AG$6:$AG$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$AG$6:$AG$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),FILTER('Master Schedule'!$J$6:$J$500,('Master Schedule'!$AG$6:$AG$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),FILTER('Master Schedule'!$AG$6:$AG$500,('Master Schedule'!$AG$6:$AG$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),FILTER('Master Schedule'!$AH$6:$AH$500,('Master Schedule'!$AG$6:$AG$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),FILTER('Master Schedule'!$AI$6:$AI$500,('Master Schedule'!$AG$6:$AG$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),FILTER('Master Schedule'!$AJ$6:$AJ$500,('Master Schedule'!$AG$6:$AG$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;""))),FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$AG$6:$AG$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$AG$6:$AG$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"No jobs in queue")</f>
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn.HSTACK(_xlfn.SEQUENCE(ROWS(_xlfn._xlws.FILTER('Master Schedule'!$A$6:$A$500,('Master Schedule'!$AG$6:$AG$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")))),_xlfn._xlws.FILTER('Master Schedule'!$A$6:$A$500,('Master Schedule'!$AG$6:$AG$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$B$6:$B$500,('Master Schedule'!$AG$6:$AG$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$C$6:$C$500,('Master Schedule'!$AG$6:$AG$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$E$6:$E$500,('Master Schedule'!$AG$6:$AG$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$F$6:$F$500,('Master Schedule'!$AG$6:$AG$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$AG$6:$AG$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$J$6:$J$500,('Master Schedule'!$AG$6:$AG$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$AG$6:$AG$500,('Master Schedule'!$AG$6:$AG$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$AH$6:$AH$500,('Master Schedule'!$AG$6:$AG$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$AI$6:$AI$500,('Master Schedule'!$AG$6:$AG$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$AJ$6:$AJ$500,('Master Schedule'!$AG$6:$AG$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;""))),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$AG$6:$AG$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$AG$6:$AG$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"No jobs in queue")</f>
         <v/>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
     </row>
     <row r="8">
       <c r="A8">
-        <f>IFERROR(SORTBY(HSTACK(SEQUENCE(ROWS(FILTER('Master Schedule'!$A$6:$A$500,('Master Schedule'!$AK$6:$AK$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")))),FILTER('Master Schedule'!$A$6:$A$500,('Master Schedule'!$AK$6:$AK$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),FILTER('Master Schedule'!$B$6:$B$500,('Master Schedule'!$AK$6:$AK$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),FILTER('Master Schedule'!$C$6:$C$500,('Master Schedule'!$AK$6:$AK$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),FILTER('Master Schedule'!$E$6:$E$500,('Master Schedule'!$AK$6:$AK$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),FILTER('Master Schedule'!$F$6:$F$500,('Master Schedule'!$AK$6:$AK$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$AK$6:$AK$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),FILTER('Master Schedule'!$J$6:$J$500,('Master Schedule'!$AK$6:$AK$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),FILTER('Master Schedule'!$AK$6:$AK$500,('Master Schedule'!$AK$6:$AK$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),FILTER('Master Schedule'!$AL$6:$AL$500,('Master Schedule'!$AK$6:$AK$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),FILTER('Master Schedule'!$AM$6:$AM$500,('Master Schedule'!$AK$6:$AK$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),FILTER('Master Schedule'!$AN$6:$AN$500,('Master Schedule'!$AK$6:$AK$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;""))),FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$AK$6:$AK$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$AK$6:$AK$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"No jobs in queue")</f>
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn.HSTACK(_xlfn.SEQUENCE(ROWS(_xlfn._xlws.FILTER('Master Schedule'!$A$6:$A$500,('Master Schedule'!$AK$6:$AK$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")))),_xlfn._xlws.FILTER('Master Schedule'!$A$6:$A$500,('Master Schedule'!$AK$6:$AK$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$B$6:$B$500,('Master Schedule'!$AK$6:$AK$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$C$6:$C$500,('Master Schedule'!$AK$6:$AK$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$E$6:$E$500,('Master Schedule'!$AK$6:$AK$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$F$6:$F$500,('Master Schedule'!$AK$6:$AK$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$AK$6:$AK$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$J$6:$J$500,('Master Schedule'!$AK$6:$AK$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$AK$6:$AK$500,('Master Schedule'!$AK$6:$AK$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$AL$6:$AL$500,('Master Schedule'!$AK$6:$AK$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$AM$6:$AM$500,('Master Schedule'!$AK$6:$AK$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$AN$6:$AN$500,('Master Schedule'!$AK$6:$AK$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;""))),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$AK$6:$AK$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$AK$6:$AK$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"No jobs in queue")</f>
         <v/>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
     </row>
     <row r="8">
       <c r="A8">
-        <f>IFERROR(SORTBY(HSTACK(SEQUENCE(ROWS(FILTER('Master Schedule'!$A$6:$A$500,('Master Schedule'!$AO$6:$AO$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")))),FILTER('Master Schedule'!$A$6:$A$500,('Master Schedule'!$AO$6:$AO$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),FILTER('Master Schedule'!$B$6:$B$500,('Master Schedule'!$AO$6:$AO$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),FILTER('Master Schedule'!$C$6:$C$500,('Master Schedule'!$AO$6:$AO$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),FILTER('Master Schedule'!$E$6:$E$500,('Master Schedule'!$AO$6:$AO$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),FILTER('Master Schedule'!$F$6:$F$500,('Master Schedule'!$AO$6:$AO$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$AO$6:$AO$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),FILTER('Master Schedule'!$J$6:$J$500,('Master Schedule'!$AO$6:$AO$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),FILTER('Master Schedule'!$AO$6:$AO$500,('Master Schedule'!$AO$6:$AO$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),FILTER('Master Schedule'!$AP$6:$AP$500,('Master Schedule'!$AO$6:$AO$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),FILTER('Master Schedule'!$AQ$6:$AQ$500,('Master Schedule'!$AO$6:$AO$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),FILTER('Master Schedule'!$AR$6:$AR$500,('Master Schedule'!$AO$6:$AO$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;""))),FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$AO$6:$AO$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$AO$6:$AO$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"No jobs in queue")</f>
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn.HSTACK(_xlfn.SEQUENCE(ROWS(_xlfn._xlws.FILTER('Master Schedule'!$A$6:$A$500,('Master Schedule'!$AO$6:$AO$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")))),_xlfn._xlws.FILTER('Master Schedule'!$A$6:$A$500,('Master Schedule'!$AO$6:$AO$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$B$6:$B$500,('Master Schedule'!$AO$6:$AO$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$C$6:$C$500,('Master Schedule'!$AO$6:$AO$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$E$6:$E$500,('Master Schedule'!$AO$6:$AO$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$F$6:$F$500,('Master Schedule'!$AO$6:$AO$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$AO$6:$AO$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$J$6:$J$500,('Master Schedule'!$AO$6:$AO$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$AO$6:$AO$500,('Master Schedule'!$AO$6:$AO$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$AP$6:$AP$500,('Master Schedule'!$AO$6:$AO$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$AQ$6:$AQ$500,('Master Schedule'!$AO$6:$AO$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$AR$6:$AR$500,('Master Schedule'!$AO$6:$AO$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;""))),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$AO$6:$AO$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$AO$6:$AO$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"No jobs in queue")</f>
         <v/>
       </c>
     </row>
@@ -1778,7 +1778,7 @@
     </row>
     <row r="8">
       <c r="A8">
-        <f>IFERROR(SORTBY(HSTACK(SEQUENCE(ROWS(FILTER('Master Schedule'!$A$6:$A$500,('Master Schedule'!$AS$6:$AS$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")))),FILTER('Master Schedule'!$A$6:$A$500,('Master Schedule'!$AS$6:$AS$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),FILTER('Master Schedule'!$B$6:$B$500,('Master Schedule'!$AS$6:$AS$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),FILTER('Master Schedule'!$C$6:$C$500,('Master Schedule'!$AS$6:$AS$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),FILTER('Master Schedule'!$E$6:$E$500,('Master Schedule'!$AS$6:$AS$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),FILTER('Master Schedule'!$F$6:$F$500,('Master Schedule'!$AS$6:$AS$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$AS$6:$AS$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),FILTER('Master Schedule'!$J$6:$J$500,('Master Schedule'!$AS$6:$AS$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),FILTER('Master Schedule'!$AS$6:$AS$500,('Master Schedule'!$AS$6:$AS$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),FILTER('Master Schedule'!$AT$6:$AT$500,('Master Schedule'!$AS$6:$AS$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),FILTER('Master Schedule'!$AU$6:$AU$500,('Master Schedule'!$AS$6:$AS$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),FILTER('Master Schedule'!$AV$6:$AV$500,('Master Schedule'!$AS$6:$AS$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;""))),FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$AS$6:$AS$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$AS$6:$AS$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"No jobs in queue")</f>
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn.HSTACK(_xlfn.SEQUENCE(ROWS(_xlfn._xlws.FILTER('Master Schedule'!$A$6:$A$500,('Master Schedule'!$AS$6:$AS$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")))),_xlfn._xlws.FILTER('Master Schedule'!$A$6:$A$500,('Master Schedule'!$AS$6:$AS$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$B$6:$B$500,('Master Schedule'!$AS$6:$AS$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$C$6:$C$500,('Master Schedule'!$AS$6:$AS$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$E$6:$E$500,('Master Schedule'!$AS$6:$AS$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$F$6:$F$500,('Master Schedule'!$AS$6:$AS$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$AS$6:$AS$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$J$6:$J$500,('Master Schedule'!$AS$6:$AS$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$AS$6:$AS$500,('Master Schedule'!$AS$6:$AS$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$AT$6:$AT$500,('Master Schedule'!$AS$6:$AS$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$AU$6:$AU$500,('Master Schedule'!$AS$6:$AS$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$AV$6:$AV$500,('Master Schedule'!$AS$6:$AS$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;""))),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$AS$6:$AS$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$AS$6:$AS$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"No jobs in queue")</f>
         <v/>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
     </row>
     <row r="8">
       <c r="A8">
-        <f>IFERROR(SORTBY(HSTACK(SEQUENCE(ROWS(FILTER('Master Schedule'!$A$6:$A$500,('Master Schedule'!$AW$6:$AW$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")))),FILTER('Master Schedule'!$A$6:$A$500,('Master Schedule'!$AW$6:$AW$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),FILTER('Master Schedule'!$B$6:$B$500,('Master Schedule'!$AW$6:$AW$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),FILTER('Master Schedule'!$C$6:$C$500,('Master Schedule'!$AW$6:$AW$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),FILTER('Master Schedule'!$E$6:$E$500,('Master Schedule'!$AW$6:$AW$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),FILTER('Master Schedule'!$F$6:$F$500,('Master Schedule'!$AW$6:$AW$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$AW$6:$AW$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),FILTER('Master Schedule'!$J$6:$J$500,('Master Schedule'!$AW$6:$AW$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),FILTER('Master Schedule'!$AW$6:$AW$500,('Master Schedule'!$AW$6:$AW$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),FILTER('Master Schedule'!$AX$6:$AX$500,('Master Schedule'!$AW$6:$AW$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),FILTER('Master Schedule'!$AY$6:$AY$500,('Master Schedule'!$AW$6:$AW$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),FILTER('Master Schedule'!$AZ$6:$AZ$500,('Master Schedule'!$AW$6:$AW$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;""))),FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$AW$6:$AW$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$AW$6:$AW$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"No jobs in queue")</f>
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn.HSTACK(_xlfn.SEQUENCE(ROWS(_xlfn._xlws.FILTER('Master Schedule'!$A$6:$A$500,('Master Schedule'!$AW$6:$AW$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")))),_xlfn._xlws.FILTER('Master Schedule'!$A$6:$A$500,('Master Schedule'!$AW$6:$AW$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$B$6:$B$500,('Master Schedule'!$AW$6:$AW$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$C$6:$C$500,('Master Schedule'!$AW$6:$AW$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$E$6:$E$500,('Master Schedule'!$AW$6:$AW$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$F$6:$F$500,('Master Schedule'!$AW$6:$AW$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$AW$6:$AW$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$J$6:$J$500,('Master Schedule'!$AW$6:$AW$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$AW$6:$AW$500,('Master Schedule'!$AW$6:$AW$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$AX$6:$AX$500,('Master Schedule'!$AW$6:$AW$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$AY$6:$AY$500,('Master Schedule'!$AW$6:$AW$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$AZ$6:$AZ$500,('Master Schedule'!$AW$6:$AW$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;""))),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$AW$6:$AW$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$AW$6:$AW$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"No jobs in queue")</f>
         <v/>
       </c>
     </row>
@@ -2094,7 +2094,7 @@
     </row>
     <row r="8">
       <c r="A8">
-        <f>IFERROR(SORTBY(HSTACK(SEQUENCE(ROWS(FILTER('Master Schedule'!$A$6:$A$500,('Master Schedule'!$BA$6:$BA$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")))),FILTER('Master Schedule'!$A$6:$A$500,('Master Schedule'!$BA$6:$BA$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),FILTER('Master Schedule'!$B$6:$B$500,('Master Schedule'!$BA$6:$BA$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),FILTER('Master Schedule'!$C$6:$C$500,('Master Schedule'!$BA$6:$BA$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),FILTER('Master Schedule'!$E$6:$E$500,('Master Schedule'!$BA$6:$BA$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),FILTER('Master Schedule'!$F$6:$F$500,('Master Schedule'!$BA$6:$BA$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$BA$6:$BA$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),FILTER('Master Schedule'!$J$6:$J$500,('Master Schedule'!$BA$6:$BA$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),FILTER('Master Schedule'!$BA$6:$BA$500,('Master Schedule'!$BA$6:$BA$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),FILTER('Master Schedule'!$BB$6:$BB$500,('Master Schedule'!$BA$6:$BA$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),FILTER('Master Schedule'!$BC$6:$BC$500,('Master Schedule'!$BA$6:$BA$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),FILTER('Master Schedule'!$BD$6:$BD$500,('Master Schedule'!$BA$6:$BA$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;""))),FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$BA$6:$BA$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$BA$6:$BA$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"No jobs in queue")</f>
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn.HSTACK(_xlfn.SEQUENCE(ROWS(_xlfn._xlws.FILTER('Master Schedule'!$A$6:$A$500,('Master Schedule'!$BA$6:$BA$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")))),_xlfn._xlws.FILTER('Master Schedule'!$A$6:$A$500,('Master Schedule'!$BA$6:$BA$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$B$6:$B$500,('Master Schedule'!$BA$6:$BA$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$C$6:$C$500,('Master Schedule'!$BA$6:$BA$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$E$6:$E$500,('Master Schedule'!$BA$6:$BA$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$F$6:$F$500,('Master Schedule'!$BA$6:$BA$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$BA$6:$BA$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$J$6:$J$500,('Master Schedule'!$BA$6:$BA$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$BA$6:$BA$500,('Master Schedule'!$BA$6:$BA$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$BB$6:$BB$500,('Master Schedule'!$BA$6:$BA$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$BC$6:$BC$500,('Master Schedule'!$BA$6:$BA$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$BD$6:$BD$500,('Master Schedule'!$BA$6:$BA$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;""))),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$BA$6:$BA$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$BA$6:$BA$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"No jobs in queue")</f>
         <v/>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
     </row>
     <row r="8">
       <c r="A8">
-        <f>IFERROR(SORTBY(HSTACK(SEQUENCE(ROWS(FILTER('Master Schedule'!$A$6:$A$500,('Master Schedule'!$BE$6:$BE$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")))),FILTER('Master Schedule'!$A$6:$A$500,('Master Schedule'!$BE$6:$BE$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),FILTER('Master Schedule'!$B$6:$B$500,('Master Schedule'!$BE$6:$BE$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),FILTER('Master Schedule'!$C$6:$C$500,('Master Schedule'!$BE$6:$BE$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),FILTER('Master Schedule'!$E$6:$E$500,('Master Schedule'!$BE$6:$BE$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),FILTER('Master Schedule'!$F$6:$F$500,('Master Schedule'!$BE$6:$BE$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$BE$6:$BE$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),FILTER('Master Schedule'!$J$6:$J$500,('Master Schedule'!$BE$6:$BE$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),FILTER('Master Schedule'!$BE$6:$BE$500,('Master Schedule'!$BE$6:$BE$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),FILTER('Master Schedule'!$BF$6:$BF$500,('Master Schedule'!$BE$6:$BE$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),FILTER('Master Schedule'!$BG$6:$BG$500,('Master Schedule'!$BE$6:$BE$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),FILTER('Master Schedule'!$BH$6:$BH$500,('Master Schedule'!$BE$6:$BE$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;""))),FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$BE$6:$BE$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$BE$6:$BE$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"No jobs in queue")</f>
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn.HSTACK(_xlfn.SEQUENCE(ROWS(_xlfn._xlws.FILTER('Master Schedule'!$A$6:$A$500,('Master Schedule'!$BE$6:$BE$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")))),_xlfn._xlws.FILTER('Master Schedule'!$A$6:$A$500,('Master Schedule'!$BE$6:$BE$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$B$6:$B$500,('Master Schedule'!$BE$6:$BE$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$C$6:$C$500,('Master Schedule'!$BE$6:$BE$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$E$6:$E$500,('Master Schedule'!$BE$6:$BE$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$F$6:$F$500,('Master Schedule'!$BE$6:$BE$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$BE$6:$BE$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$J$6:$J$500,('Master Schedule'!$BE$6:$BE$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$BE$6:$BE$500,('Master Schedule'!$BE$6:$BE$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$BF$6:$BF$500,('Master Schedule'!$BE$6:$BE$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$BG$6:$BG$500,('Master Schedule'!$BE$6:$BE$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$BH$6:$BH$500,('Master Schedule'!$BE$6:$BE$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;""))),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$BE$6:$BE$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$BE$6:$BE$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"No jobs in queue")</f>
         <v/>
       </c>
     </row>
@@ -2410,7 +2410,7 @@
     </row>
     <row r="8">
       <c r="A8">
-        <f>IFERROR(SORTBY(HSTACK(SEQUENCE(ROWS(FILTER('Master Schedule'!$A$6:$A$500,('Master Schedule'!$BI$6:$BI$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")))),FILTER('Master Schedule'!$A$6:$A$500,('Master Schedule'!$BI$6:$BI$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),FILTER('Master Schedule'!$B$6:$B$500,('Master Schedule'!$BI$6:$BI$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),FILTER('Master Schedule'!$C$6:$C$500,('Master Schedule'!$BI$6:$BI$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),FILTER('Master Schedule'!$E$6:$E$500,('Master Schedule'!$BI$6:$BI$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),FILTER('Master Schedule'!$F$6:$F$500,('Master Schedule'!$BI$6:$BI$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$BI$6:$BI$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),FILTER('Master Schedule'!$J$6:$J$500,('Master Schedule'!$BI$6:$BI$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),FILTER('Master Schedule'!$BI$6:$BI$500,('Master Schedule'!$BI$6:$BI$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),FILTER('Master Schedule'!$BJ$6:$BJ$500,('Master Schedule'!$BI$6:$BI$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),FILTER('Master Schedule'!$BK$6:$BK$500,('Master Schedule'!$BI$6:$BI$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),FILTER('Master Schedule'!$BL$6:$BL$500,('Master Schedule'!$BI$6:$BI$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;""))),FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$BI$6:$BI$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$BI$6:$BI$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"No jobs in queue")</f>
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn.HSTACK(_xlfn.SEQUENCE(ROWS(_xlfn._xlws.FILTER('Master Schedule'!$A$6:$A$500,('Master Schedule'!$BI$6:$BI$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")))),_xlfn._xlws.FILTER('Master Schedule'!$A$6:$A$500,('Master Schedule'!$BI$6:$BI$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$B$6:$B$500,('Master Schedule'!$BI$6:$BI$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$C$6:$C$500,('Master Schedule'!$BI$6:$BI$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$E$6:$E$500,('Master Schedule'!$BI$6:$BI$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$F$6:$F$500,('Master Schedule'!$BI$6:$BI$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$BI$6:$BI$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$J$6:$J$500,('Master Schedule'!$BI$6:$BI$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$BI$6:$BI$500,('Master Schedule'!$BI$6:$BI$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$BJ$6:$BJ$500,('Master Schedule'!$BI$6:$BI$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$BK$6:$BK$500,('Master Schedule'!$BI$6:$BI$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$BL$6:$BL$500,('Master Schedule'!$BI$6:$BI$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;""))),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$BI$6:$BI$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$BI$6:$BI$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"No jobs in queue")</f>
         <v/>
       </c>
     </row>
@@ -8318,7 +8318,7 @@
     </row>
     <row r="8">
       <c r="A8">
-        <f>IFERROR(SORTBY(HSTACK(SEQUENCE(ROWS(FILTER('Master Schedule'!$A$6:$A$500,('Master Schedule'!$A$6:$A$500&lt;&gt;"")*IF($B$4="All",1,ISNUMBER(SEARCH($B$4,'Master Schedule'!$A$6:$A$500)))*IF($D$4="All",1,'Master Schedule'!$F$6:$F$500=$D$4)))),FILTER('Master Schedule'!$A$6:$A$500,('Master Schedule'!$A$6:$A$500&lt;&gt;"")*IF($D$4="All",1,'Master Schedule'!$F$6:$F$500=$D$4)),FILTER('Master Schedule'!$B$6:$B$500,('Master Schedule'!$A$6:$A$500&lt;&gt;"")*IF($D$4="All",1,'Master Schedule'!$F$6:$F$500=$D$4)),FILTER('Master Schedule'!$C$6:$C$500,('Master Schedule'!$A$6:$A$500&lt;&gt;"")*IF($D$4="All",1,'Master Schedule'!$F$6:$F$500=$D$4)),FILTER('Master Schedule'!$E$6:$E$500,('Master Schedule'!$A$6:$A$500&lt;&gt;"")*IF($D$4="All",1,'Master Schedule'!$F$6:$F$500=$D$4)),FILTER('Master Schedule'!$F$6:$F$500,('Master Schedule'!$A$6:$A$500&lt;&gt;"")*IF($D$4="All",1,'Master Schedule'!$F$6:$F$500=$D$4)),FILTER('Master Schedule'!$G$6:$G$500,('Master Schedule'!$A$6:$A$500&lt;&gt;"")*IF($D$4="All",1,'Master Schedule'!$F$6:$F$500=$D$4)),FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$A$6:$A$500&lt;&gt;"")*IF($D$4="All",1,'Master Schedule'!$F$6:$F$500=$D$4)),FILTER('Master Schedule'!$J$6:$J$500,('Master Schedule'!$A$6:$A$500&lt;&gt;"")*IF($D$4="All",1,'Master Schedule'!$F$6:$F$500=$D$4)),FILTER('Master Schedule'!$G$6:$G$500,('Master Schedule'!$A$6:$A$500&lt;&gt;"")*IF($D$4="All",1,'Master Schedule'!$F$6:$F$500=$D$4)),FILTER('Master Schedule'!$L$6:$L$500,('Master Schedule'!$A$6:$A$500&lt;&gt;"")*IF($D$4="All",1,'Master Schedule'!$F$6:$F$500=$D$4))),FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$A$6:$A$500&lt;&gt;"")*IF($D$4="All",1,'Master Schedule'!$F$6:$F$500=$D$4)),1,FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$A$6:$A$500&lt;&gt;"")*IF($D$4="All",1,'Master Schedule'!$F$6:$F$500=$D$4)),1),"No jobs match")</f>
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn.HSTACK(_xlfn.SEQUENCE(ROWS(_xlfn._xlws.FILTER('Master Schedule'!$A$6:$A$500,('Master Schedule'!$A$6:$A$500&lt;&gt;"")*IF($B$4="All",1,ISNUMBER(SEARCH($B$4,'Master Schedule'!$A$6:$A$500)))*IF($D$4="All",1,'Master Schedule'!$F$6:$F$500=$D$4)))),_xlfn._xlws.FILTER('Master Schedule'!$A$6:$A$500,('Master Schedule'!$A$6:$A$500&lt;&gt;"")*IF($D$4="All",1,'Master Schedule'!$F$6:$F$500=$D$4)),_xlfn._xlws.FILTER('Master Schedule'!$B$6:$B$500,('Master Schedule'!$A$6:$A$500&lt;&gt;"")*IF($D$4="All",1,'Master Schedule'!$F$6:$F$500=$D$4)),_xlfn._xlws.FILTER('Master Schedule'!$C$6:$C$500,('Master Schedule'!$A$6:$A$500&lt;&gt;"")*IF($D$4="All",1,'Master Schedule'!$F$6:$F$500=$D$4)),_xlfn._xlws.FILTER('Master Schedule'!$E$6:$E$500,('Master Schedule'!$A$6:$A$500&lt;&gt;"")*IF($D$4="All",1,'Master Schedule'!$F$6:$F$500=$D$4)),_xlfn._xlws.FILTER('Master Schedule'!$F$6:$F$500,('Master Schedule'!$A$6:$A$500&lt;&gt;"")*IF($D$4="All",1,'Master Schedule'!$F$6:$F$500=$D$4)),_xlfn._xlws.FILTER('Master Schedule'!$G$6:$G$500,('Master Schedule'!$A$6:$A$500&lt;&gt;"")*IF($D$4="All",1,'Master Schedule'!$F$6:$F$500=$D$4)),_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$A$6:$A$500&lt;&gt;"")*IF($D$4="All",1,'Master Schedule'!$F$6:$F$500=$D$4)),_xlfn._xlws.FILTER('Master Schedule'!$J$6:$J$500,('Master Schedule'!$A$6:$A$500&lt;&gt;"")*IF($D$4="All",1,'Master Schedule'!$F$6:$F$500=$D$4)),_xlfn._xlws.FILTER('Master Schedule'!$G$6:$G$500,('Master Schedule'!$A$6:$A$500&lt;&gt;"")*IF($D$4="All",1,'Master Schedule'!$F$6:$F$500=$D$4)),_xlfn._xlws.FILTER('Master Schedule'!$L$6:$L$500,('Master Schedule'!$A$6:$A$500&lt;&gt;"")*IF($D$4="All",1,'Master Schedule'!$F$6:$F$500=$D$4))),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$A$6:$A$500&lt;&gt;"")*IF($D$4="All",1,'Master Schedule'!$F$6:$F$500=$D$4)),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$A$6:$A$500&lt;&gt;"")*IF($D$4="All",1,'Master Schedule'!$F$6:$F$500=$D$4)),1),"No jobs match")</f>
         <v/>
       </c>
     </row>
@@ -8477,7 +8477,7 @@
     </row>
     <row r="8">
       <c r="A8">
-        <f>IFERROR(SORTBY(HSTACK(SEQUENCE(ROWS(FILTER('Master Schedule'!$A$6:$A$500,('Master Schedule'!$M$6:$M$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")))),FILTER('Master Schedule'!$A$6:$A$500,('Master Schedule'!$M$6:$M$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),FILTER('Master Schedule'!$B$6:$B$500,('Master Schedule'!$M$6:$M$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),FILTER('Master Schedule'!$C$6:$C$500,('Master Schedule'!$M$6:$M$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),FILTER('Master Schedule'!$E$6:$E$500,('Master Schedule'!$M$6:$M$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),FILTER('Master Schedule'!$F$6:$F$500,('Master Schedule'!$M$6:$M$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$M$6:$M$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),FILTER('Master Schedule'!$J$6:$J$500,('Master Schedule'!$M$6:$M$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),FILTER('Master Schedule'!$M$6:$M$500,('Master Schedule'!$M$6:$M$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),FILTER('Master Schedule'!$N$6:$N$500,('Master Schedule'!$M$6:$M$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),FILTER('Master Schedule'!$O$6:$O$500,('Master Schedule'!$M$6:$M$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),FILTER('Master Schedule'!$P$6:$P$500,('Master Schedule'!$M$6:$M$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;""))),FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$M$6:$M$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$M$6:$M$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"No jobs in queue")</f>
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn.HSTACK(_xlfn.SEQUENCE(ROWS(_xlfn._xlws.FILTER('Master Schedule'!$A$6:$A$500,('Master Schedule'!$M$6:$M$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")))),_xlfn._xlws.FILTER('Master Schedule'!$A$6:$A$500,('Master Schedule'!$M$6:$M$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$B$6:$B$500,('Master Schedule'!$M$6:$M$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$C$6:$C$500,('Master Schedule'!$M$6:$M$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$E$6:$E$500,('Master Schedule'!$M$6:$M$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$F$6:$F$500,('Master Schedule'!$M$6:$M$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$M$6:$M$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$J$6:$J$500,('Master Schedule'!$M$6:$M$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$M$6:$M$500,('Master Schedule'!$M$6:$M$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$N$6:$N$500,('Master Schedule'!$M$6:$M$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$O$6:$O$500,('Master Schedule'!$M$6:$M$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$P$6:$P$500,('Master Schedule'!$M$6:$M$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;""))),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$M$6:$M$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$M$6:$M$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"No jobs in queue")</f>
         <v/>
       </c>
     </row>
@@ -8635,7 +8635,7 @@
     </row>
     <row r="8">
       <c r="A8">
-        <f>IFERROR(SORTBY(HSTACK(SEQUENCE(ROWS(FILTER('Master Schedule'!$A$6:$A$500,('Master Schedule'!$Q$6:$Q$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")))),FILTER('Master Schedule'!$A$6:$A$500,('Master Schedule'!$Q$6:$Q$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),FILTER('Master Schedule'!$B$6:$B$500,('Master Schedule'!$Q$6:$Q$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),FILTER('Master Schedule'!$C$6:$C$500,('Master Schedule'!$Q$6:$Q$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),FILTER('Master Schedule'!$E$6:$E$500,('Master Schedule'!$Q$6:$Q$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),FILTER('Master Schedule'!$F$6:$F$500,('Master Schedule'!$Q$6:$Q$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$Q$6:$Q$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),FILTER('Master Schedule'!$J$6:$J$500,('Master Schedule'!$Q$6:$Q$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),FILTER('Master Schedule'!$Q$6:$Q$500,('Master Schedule'!$Q$6:$Q$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),FILTER('Master Schedule'!$R$6:$R$500,('Master Schedule'!$Q$6:$Q$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),FILTER('Master Schedule'!$S$6:$S$500,('Master Schedule'!$Q$6:$Q$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),FILTER('Master Schedule'!$T$6:$T$500,('Master Schedule'!$Q$6:$Q$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;""))),FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$Q$6:$Q$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$Q$6:$Q$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"No jobs in queue")</f>
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn.HSTACK(_xlfn.SEQUENCE(ROWS(_xlfn._xlws.FILTER('Master Schedule'!$A$6:$A$500,('Master Schedule'!$Q$6:$Q$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")))),_xlfn._xlws.FILTER('Master Schedule'!$A$6:$A$500,('Master Schedule'!$Q$6:$Q$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$B$6:$B$500,('Master Schedule'!$Q$6:$Q$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$C$6:$C$500,('Master Schedule'!$Q$6:$Q$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$E$6:$E$500,('Master Schedule'!$Q$6:$Q$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$F$6:$F$500,('Master Schedule'!$Q$6:$Q$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$Q$6:$Q$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$J$6:$J$500,('Master Schedule'!$Q$6:$Q$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$Q$6:$Q$500,('Master Schedule'!$Q$6:$Q$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$R$6:$R$500,('Master Schedule'!$Q$6:$Q$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$S$6:$S$500,('Master Schedule'!$Q$6:$Q$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$T$6:$T$500,('Master Schedule'!$Q$6:$Q$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;""))),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$Q$6:$Q$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$Q$6:$Q$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"No jobs in queue")</f>
         <v/>
       </c>
     </row>
@@ -8793,7 +8793,7 @@
     </row>
     <row r="8">
       <c r="A8">
-        <f>IFERROR(SORTBY(HSTACK(SEQUENCE(ROWS(FILTER('Master Schedule'!$A$6:$A$500,('Master Schedule'!$U$6:$U$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")))),FILTER('Master Schedule'!$A$6:$A$500,('Master Schedule'!$U$6:$U$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),FILTER('Master Schedule'!$B$6:$B$500,('Master Schedule'!$U$6:$U$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),FILTER('Master Schedule'!$C$6:$C$500,('Master Schedule'!$U$6:$U$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),FILTER('Master Schedule'!$E$6:$E$500,('Master Schedule'!$U$6:$U$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),FILTER('Master Schedule'!$F$6:$F$500,('Master Schedule'!$U$6:$U$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$U$6:$U$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),FILTER('Master Schedule'!$J$6:$J$500,('Master Schedule'!$U$6:$U$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),FILTER('Master Schedule'!$U$6:$U$500,('Master Schedule'!$U$6:$U$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),FILTER('Master Schedule'!$V$6:$V$500,('Master Schedule'!$U$6:$U$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),FILTER('Master Schedule'!$W$6:$W$500,('Master Schedule'!$U$6:$U$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),FILTER('Master Schedule'!$X$6:$X$500,('Master Schedule'!$U$6:$U$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;""))),FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$U$6:$U$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$U$6:$U$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"No jobs in queue")</f>
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn.HSTACK(_xlfn.SEQUENCE(ROWS(_xlfn._xlws.FILTER('Master Schedule'!$A$6:$A$500,('Master Schedule'!$U$6:$U$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")))),_xlfn._xlws.FILTER('Master Schedule'!$A$6:$A$500,('Master Schedule'!$U$6:$U$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$B$6:$B$500,('Master Schedule'!$U$6:$U$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$C$6:$C$500,('Master Schedule'!$U$6:$U$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$E$6:$E$500,('Master Schedule'!$U$6:$U$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$F$6:$F$500,('Master Schedule'!$U$6:$U$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$U$6:$U$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$J$6:$J$500,('Master Schedule'!$U$6:$U$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$U$6:$U$500,('Master Schedule'!$U$6:$U$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$V$6:$V$500,('Master Schedule'!$U$6:$U$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$W$6:$W$500,('Master Schedule'!$U$6:$U$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$X$6:$X$500,('Master Schedule'!$U$6:$U$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;""))),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$U$6:$U$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$U$6:$U$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"No jobs in queue")</f>
         <v/>
       </c>
     </row>
@@ -8951,7 +8951,7 @@
     </row>
     <row r="8">
       <c r="A8">
-        <f>IFERROR(SORTBY(HSTACK(SEQUENCE(ROWS(FILTER('Master Schedule'!$A$6:$A$500,('Master Schedule'!$Y$6:$Y$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")))),FILTER('Master Schedule'!$A$6:$A$500,('Master Schedule'!$Y$6:$Y$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),FILTER('Master Schedule'!$B$6:$B$500,('Master Schedule'!$Y$6:$Y$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),FILTER('Master Schedule'!$C$6:$C$500,('Master Schedule'!$Y$6:$Y$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),FILTER('Master Schedule'!$E$6:$E$500,('Master Schedule'!$Y$6:$Y$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),FILTER('Master Schedule'!$F$6:$F$500,('Master Schedule'!$Y$6:$Y$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$Y$6:$Y$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),FILTER('Master Schedule'!$J$6:$J$500,('Master Schedule'!$Y$6:$Y$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),FILTER('Master Schedule'!$Y$6:$Y$500,('Master Schedule'!$Y$6:$Y$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),FILTER('Master Schedule'!$Z$6:$Z$500,('Master Schedule'!$Y$6:$Y$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),FILTER('Master Schedule'!$AA$6:$AA$500,('Master Schedule'!$Y$6:$Y$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),FILTER('Master Schedule'!$AB$6:$AB$500,('Master Schedule'!$Y$6:$Y$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;""))),FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$Y$6:$Y$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$Y$6:$Y$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"No jobs in queue")</f>
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn.HSTACK(_xlfn.SEQUENCE(ROWS(_xlfn._xlws.FILTER('Master Schedule'!$A$6:$A$500,('Master Schedule'!$Y$6:$Y$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")))),_xlfn._xlws.FILTER('Master Schedule'!$A$6:$A$500,('Master Schedule'!$Y$6:$Y$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$B$6:$B$500,('Master Schedule'!$Y$6:$Y$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$C$6:$C$500,('Master Schedule'!$Y$6:$Y$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$E$6:$E$500,('Master Schedule'!$Y$6:$Y$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$F$6:$F$500,('Master Schedule'!$Y$6:$Y$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$Y$6:$Y$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$J$6:$J$500,('Master Schedule'!$Y$6:$Y$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$Y$6:$Y$500,('Master Schedule'!$Y$6:$Y$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$Z$6:$Z$500,('Master Schedule'!$Y$6:$Y$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$AA$6:$AA$500,('Master Schedule'!$Y$6:$Y$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$AB$6:$AB$500,('Master Schedule'!$Y$6:$Y$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;""))),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$Y$6:$Y$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$Y$6:$Y$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"No jobs in queue")</f>
         <v/>
       </c>
     </row>
@@ -9109,7 +9109,7 @@
     </row>
     <row r="8">
       <c r="A8">
-        <f>IFERROR(SORTBY(HSTACK(SEQUENCE(ROWS(FILTER('Master Schedule'!$A$6:$A$500,('Master Schedule'!$AC$6:$AC$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")))),FILTER('Master Schedule'!$A$6:$A$500,('Master Schedule'!$AC$6:$AC$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),FILTER('Master Schedule'!$B$6:$B$500,('Master Schedule'!$AC$6:$AC$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),FILTER('Master Schedule'!$C$6:$C$500,('Master Schedule'!$AC$6:$AC$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),FILTER('Master Schedule'!$E$6:$E$500,('Master Schedule'!$AC$6:$AC$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),FILTER('Master Schedule'!$F$6:$F$500,('Master Schedule'!$AC$6:$AC$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$AC$6:$AC$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),FILTER('Master Schedule'!$J$6:$J$500,('Master Schedule'!$AC$6:$AC$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),FILTER('Master Schedule'!$AC$6:$AC$500,('Master Schedule'!$AC$6:$AC$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),FILTER('Master Schedule'!$AD$6:$AD$500,('Master Schedule'!$AC$6:$AC$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),FILTER('Master Schedule'!$AE$6:$AE$500,('Master Schedule'!$AC$6:$AC$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),FILTER('Master Schedule'!$AF$6:$AF$500,('Master Schedule'!$AC$6:$AC$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;""))),FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$AC$6:$AC$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$AC$6:$AC$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"No jobs in queue")</f>
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn.HSTACK(_xlfn.SEQUENCE(ROWS(_xlfn._xlws.FILTER('Master Schedule'!$A$6:$A$500,('Master Schedule'!$AC$6:$AC$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")))),_xlfn._xlws.FILTER('Master Schedule'!$A$6:$A$500,('Master Schedule'!$AC$6:$AC$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$B$6:$B$500,('Master Schedule'!$AC$6:$AC$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$C$6:$C$500,('Master Schedule'!$AC$6:$AC$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$E$6:$E$500,('Master Schedule'!$AC$6:$AC$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$F$6:$F$500,('Master Schedule'!$AC$6:$AC$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$AC$6:$AC$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$J$6:$J$500,('Master Schedule'!$AC$6:$AC$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$AC$6:$AC$500,('Master Schedule'!$AC$6:$AC$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$AD$6:$AD$500,('Master Schedule'!$AC$6:$AC$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$AE$6:$AE$500,('Master Schedule'!$AC$6:$AC$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$AF$6:$AF$500,('Master Schedule'!$AC$6:$AC$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;""))),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$AC$6:$AC$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$AC$6:$AC$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"No jobs in queue")</f>
         <v/>
       </c>
     </row>

--- a/Production_Schedule.xlsx
+++ b/Production_Schedule.xlsx
@@ -1304,7 +1304,51 @@
     </row>
     <row r="8">
       <c r="A8">
-        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn.HSTACK(_xlfn.SEQUENCE(ROWS(_xlfn._xlws.FILTER('Master Schedule'!$A$6:$A$500,('Master Schedule'!$AG$6:$AG$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")))),_xlfn._xlws.FILTER('Master Schedule'!$A$6:$A$500,('Master Schedule'!$AG$6:$AG$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$B$6:$B$500,('Master Schedule'!$AG$6:$AG$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$C$6:$C$500,('Master Schedule'!$AG$6:$AG$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$E$6:$E$500,('Master Schedule'!$AG$6:$AG$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$F$6:$F$500,('Master Schedule'!$AG$6:$AG$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$AG$6:$AG$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$J$6:$J$500,('Master Schedule'!$AG$6:$AG$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$AG$6:$AG$500,('Master Schedule'!$AG$6:$AG$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$AH$6:$AH$500,('Master Schedule'!$AG$6:$AG$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$AI$6:$AI$500,('Master Schedule'!$AG$6:$AG$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$AJ$6:$AJ$500,('Master Schedule'!$AG$6:$AG$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;""))),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$AG$6:$AG$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$AG$6:$AG$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"No jobs in queue")</f>
+        <f>IFERROR(_xlfn._xlws.SEQUENCE(ROWS(_xlfn._xlws.FILTER('Master Schedule'!$A$6:$A$500,('Master Schedule'!$AG$6:$AG$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")))),"")</f>
+        <v/>
+      </c>
+      <c r="B8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$A$6:$A$500,('Master Schedule'!$AG$6:$AG$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$AG$6:$AG$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$AG$6:$AG$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"")</f>
+        <v/>
+      </c>
+      <c r="C8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$B$6:$B$500,('Master Schedule'!$AG$6:$AG$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$AG$6:$AG$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$AG$6:$AG$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"")</f>
+        <v/>
+      </c>
+      <c r="D8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$C$6:$C$500,('Master Schedule'!$AG$6:$AG$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$AG$6:$AG$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$AG$6:$AG$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"")</f>
+        <v/>
+      </c>
+      <c r="E8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$E$6:$E$500,('Master Schedule'!$AG$6:$AG$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$AG$6:$AG$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$AG$6:$AG$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"")</f>
+        <v/>
+      </c>
+      <c r="F8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$F$6:$F$500,('Master Schedule'!$AG$6:$AG$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$AG$6:$AG$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$AG$6:$AG$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"")</f>
+        <v/>
+      </c>
+      <c r="G8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$AG$6:$AG$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$AG$6:$AG$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$AG$6:$AG$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"")</f>
+        <v/>
+      </c>
+      <c r="H8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$J$6:$J$500,('Master Schedule'!$AG$6:$AG$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$AG$6:$AG$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$AG$6:$AG$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"")</f>
+        <v/>
+      </c>
+      <c r="I8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$AG$6:$AG$500,('Master Schedule'!$AG$6:$AG$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$AG$6:$AG$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$AG$6:$AG$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"")</f>
+        <v/>
+      </c>
+      <c r="J8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$AH$6:$AH$500,('Master Schedule'!$AG$6:$AG$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$AG$6:$AG$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$AG$6:$AG$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"")</f>
+        <v/>
+      </c>
+      <c r="K8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$AI$6:$AI$500,('Master Schedule'!$AG$6:$AG$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$AG$6:$AG$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$AG$6:$AG$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"")</f>
+        <v/>
+      </c>
+      <c r="L8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$AJ$6:$AJ$500,('Master Schedule'!$AG$6:$AG$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$AG$6:$AG$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$AG$6:$AG$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"")</f>
         <v/>
       </c>
     </row>
@@ -1462,7 +1506,51 @@
     </row>
     <row r="8">
       <c r="A8">
-        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn.HSTACK(_xlfn.SEQUENCE(ROWS(_xlfn._xlws.FILTER('Master Schedule'!$A$6:$A$500,('Master Schedule'!$AK$6:$AK$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")))),_xlfn._xlws.FILTER('Master Schedule'!$A$6:$A$500,('Master Schedule'!$AK$6:$AK$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$B$6:$B$500,('Master Schedule'!$AK$6:$AK$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$C$6:$C$500,('Master Schedule'!$AK$6:$AK$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$E$6:$E$500,('Master Schedule'!$AK$6:$AK$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$F$6:$F$500,('Master Schedule'!$AK$6:$AK$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$AK$6:$AK$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$J$6:$J$500,('Master Schedule'!$AK$6:$AK$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$AK$6:$AK$500,('Master Schedule'!$AK$6:$AK$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$AL$6:$AL$500,('Master Schedule'!$AK$6:$AK$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$AM$6:$AM$500,('Master Schedule'!$AK$6:$AK$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$AN$6:$AN$500,('Master Schedule'!$AK$6:$AK$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;""))),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$AK$6:$AK$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$AK$6:$AK$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"No jobs in queue")</f>
+        <f>IFERROR(_xlfn._xlws.SEQUENCE(ROWS(_xlfn._xlws.FILTER('Master Schedule'!$A$6:$A$500,('Master Schedule'!$AK$6:$AK$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")))),"")</f>
+        <v/>
+      </c>
+      <c r="B8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$A$6:$A$500,('Master Schedule'!$AK$6:$AK$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$AK$6:$AK$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$AK$6:$AK$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"")</f>
+        <v/>
+      </c>
+      <c r="C8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$B$6:$B$500,('Master Schedule'!$AK$6:$AK$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$AK$6:$AK$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$AK$6:$AK$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"")</f>
+        <v/>
+      </c>
+      <c r="D8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$C$6:$C$500,('Master Schedule'!$AK$6:$AK$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$AK$6:$AK$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$AK$6:$AK$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"")</f>
+        <v/>
+      </c>
+      <c r="E8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$E$6:$E$500,('Master Schedule'!$AK$6:$AK$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$AK$6:$AK$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$AK$6:$AK$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"")</f>
+        <v/>
+      </c>
+      <c r="F8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$F$6:$F$500,('Master Schedule'!$AK$6:$AK$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$AK$6:$AK$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$AK$6:$AK$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"")</f>
+        <v/>
+      </c>
+      <c r="G8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$AK$6:$AK$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$AK$6:$AK$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$AK$6:$AK$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"")</f>
+        <v/>
+      </c>
+      <c r="H8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$J$6:$J$500,('Master Schedule'!$AK$6:$AK$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$AK$6:$AK$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$AK$6:$AK$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"")</f>
+        <v/>
+      </c>
+      <c r="I8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$AK$6:$AK$500,('Master Schedule'!$AK$6:$AK$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$AK$6:$AK$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$AK$6:$AK$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"")</f>
+        <v/>
+      </c>
+      <c r="J8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$AL$6:$AL$500,('Master Schedule'!$AK$6:$AK$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$AK$6:$AK$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$AK$6:$AK$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"")</f>
+        <v/>
+      </c>
+      <c r="K8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$AM$6:$AM$500,('Master Schedule'!$AK$6:$AK$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$AK$6:$AK$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$AK$6:$AK$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"")</f>
+        <v/>
+      </c>
+      <c r="L8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$AN$6:$AN$500,('Master Schedule'!$AK$6:$AK$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$AK$6:$AK$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$AK$6:$AK$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"")</f>
         <v/>
       </c>
     </row>
@@ -1620,7 +1708,51 @@
     </row>
     <row r="8">
       <c r="A8">
-        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn.HSTACK(_xlfn.SEQUENCE(ROWS(_xlfn._xlws.FILTER('Master Schedule'!$A$6:$A$500,('Master Schedule'!$AO$6:$AO$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")))),_xlfn._xlws.FILTER('Master Schedule'!$A$6:$A$500,('Master Schedule'!$AO$6:$AO$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$B$6:$B$500,('Master Schedule'!$AO$6:$AO$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$C$6:$C$500,('Master Schedule'!$AO$6:$AO$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$E$6:$E$500,('Master Schedule'!$AO$6:$AO$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$F$6:$F$500,('Master Schedule'!$AO$6:$AO$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$AO$6:$AO$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$J$6:$J$500,('Master Schedule'!$AO$6:$AO$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$AO$6:$AO$500,('Master Schedule'!$AO$6:$AO$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$AP$6:$AP$500,('Master Schedule'!$AO$6:$AO$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$AQ$6:$AQ$500,('Master Schedule'!$AO$6:$AO$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$AR$6:$AR$500,('Master Schedule'!$AO$6:$AO$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;""))),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$AO$6:$AO$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$AO$6:$AO$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"No jobs in queue")</f>
+        <f>IFERROR(_xlfn._xlws.SEQUENCE(ROWS(_xlfn._xlws.FILTER('Master Schedule'!$A$6:$A$500,('Master Schedule'!$AO$6:$AO$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")))),"")</f>
+        <v/>
+      </c>
+      <c r="B8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$A$6:$A$500,('Master Schedule'!$AO$6:$AO$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$AO$6:$AO$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$AO$6:$AO$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"")</f>
+        <v/>
+      </c>
+      <c r="C8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$B$6:$B$500,('Master Schedule'!$AO$6:$AO$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$AO$6:$AO$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$AO$6:$AO$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"")</f>
+        <v/>
+      </c>
+      <c r="D8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$C$6:$C$500,('Master Schedule'!$AO$6:$AO$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$AO$6:$AO$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$AO$6:$AO$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"")</f>
+        <v/>
+      </c>
+      <c r="E8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$E$6:$E$500,('Master Schedule'!$AO$6:$AO$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$AO$6:$AO$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$AO$6:$AO$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"")</f>
+        <v/>
+      </c>
+      <c r="F8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$F$6:$F$500,('Master Schedule'!$AO$6:$AO$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$AO$6:$AO$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$AO$6:$AO$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"")</f>
+        <v/>
+      </c>
+      <c r="G8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$AO$6:$AO$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$AO$6:$AO$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$AO$6:$AO$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"")</f>
+        <v/>
+      </c>
+      <c r="H8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$J$6:$J$500,('Master Schedule'!$AO$6:$AO$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$AO$6:$AO$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$AO$6:$AO$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"")</f>
+        <v/>
+      </c>
+      <c r="I8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$AO$6:$AO$500,('Master Schedule'!$AO$6:$AO$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$AO$6:$AO$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$AO$6:$AO$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"")</f>
+        <v/>
+      </c>
+      <c r="J8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$AP$6:$AP$500,('Master Schedule'!$AO$6:$AO$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$AO$6:$AO$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$AO$6:$AO$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"")</f>
+        <v/>
+      </c>
+      <c r="K8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$AQ$6:$AQ$500,('Master Schedule'!$AO$6:$AO$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$AO$6:$AO$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$AO$6:$AO$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"")</f>
+        <v/>
+      </c>
+      <c r="L8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$AR$6:$AR$500,('Master Schedule'!$AO$6:$AO$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$AO$6:$AO$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$AO$6:$AO$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"")</f>
         <v/>
       </c>
     </row>
@@ -1778,7 +1910,51 @@
     </row>
     <row r="8">
       <c r="A8">
-        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn.HSTACK(_xlfn.SEQUENCE(ROWS(_xlfn._xlws.FILTER('Master Schedule'!$A$6:$A$500,('Master Schedule'!$AS$6:$AS$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")))),_xlfn._xlws.FILTER('Master Schedule'!$A$6:$A$500,('Master Schedule'!$AS$6:$AS$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$B$6:$B$500,('Master Schedule'!$AS$6:$AS$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$C$6:$C$500,('Master Schedule'!$AS$6:$AS$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$E$6:$E$500,('Master Schedule'!$AS$6:$AS$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$F$6:$F$500,('Master Schedule'!$AS$6:$AS$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$AS$6:$AS$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$J$6:$J$500,('Master Schedule'!$AS$6:$AS$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$AS$6:$AS$500,('Master Schedule'!$AS$6:$AS$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$AT$6:$AT$500,('Master Schedule'!$AS$6:$AS$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$AU$6:$AU$500,('Master Schedule'!$AS$6:$AS$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$AV$6:$AV$500,('Master Schedule'!$AS$6:$AS$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;""))),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$AS$6:$AS$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$AS$6:$AS$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"No jobs in queue")</f>
+        <f>IFERROR(_xlfn._xlws.SEQUENCE(ROWS(_xlfn._xlws.FILTER('Master Schedule'!$A$6:$A$500,('Master Schedule'!$AS$6:$AS$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")))),"")</f>
+        <v/>
+      </c>
+      <c r="B8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$A$6:$A$500,('Master Schedule'!$AS$6:$AS$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$AS$6:$AS$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$AS$6:$AS$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"")</f>
+        <v/>
+      </c>
+      <c r="C8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$B$6:$B$500,('Master Schedule'!$AS$6:$AS$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$AS$6:$AS$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$AS$6:$AS$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"")</f>
+        <v/>
+      </c>
+      <c r="D8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$C$6:$C$500,('Master Schedule'!$AS$6:$AS$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$AS$6:$AS$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$AS$6:$AS$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"")</f>
+        <v/>
+      </c>
+      <c r="E8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$E$6:$E$500,('Master Schedule'!$AS$6:$AS$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$AS$6:$AS$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$AS$6:$AS$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"")</f>
+        <v/>
+      </c>
+      <c r="F8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$F$6:$F$500,('Master Schedule'!$AS$6:$AS$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$AS$6:$AS$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$AS$6:$AS$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"")</f>
+        <v/>
+      </c>
+      <c r="G8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$AS$6:$AS$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$AS$6:$AS$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$AS$6:$AS$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"")</f>
+        <v/>
+      </c>
+      <c r="H8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$J$6:$J$500,('Master Schedule'!$AS$6:$AS$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$AS$6:$AS$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$AS$6:$AS$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"")</f>
+        <v/>
+      </c>
+      <c r="I8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$AS$6:$AS$500,('Master Schedule'!$AS$6:$AS$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$AS$6:$AS$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$AS$6:$AS$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"")</f>
+        <v/>
+      </c>
+      <c r="J8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$AT$6:$AT$500,('Master Schedule'!$AS$6:$AS$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$AS$6:$AS$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$AS$6:$AS$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"")</f>
+        <v/>
+      </c>
+      <c r="K8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$AU$6:$AU$500,('Master Schedule'!$AS$6:$AS$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$AS$6:$AS$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$AS$6:$AS$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"")</f>
+        <v/>
+      </c>
+      <c r="L8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$AV$6:$AV$500,('Master Schedule'!$AS$6:$AS$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$AS$6:$AS$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$AS$6:$AS$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"")</f>
         <v/>
       </c>
     </row>
@@ -1936,7 +2112,51 @@
     </row>
     <row r="8">
       <c r="A8">
-        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn.HSTACK(_xlfn.SEQUENCE(ROWS(_xlfn._xlws.FILTER('Master Schedule'!$A$6:$A$500,('Master Schedule'!$AW$6:$AW$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")))),_xlfn._xlws.FILTER('Master Schedule'!$A$6:$A$500,('Master Schedule'!$AW$6:$AW$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$B$6:$B$500,('Master Schedule'!$AW$6:$AW$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$C$6:$C$500,('Master Schedule'!$AW$6:$AW$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$E$6:$E$500,('Master Schedule'!$AW$6:$AW$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$F$6:$F$500,('Master Schedule'!$AW$6:$AW$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$AW$6:$AW$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$J$6:$J$500,('Master Schedule'!$AW$6:$AW$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$AW$6:$AW$500,('Master Schedule'!$AW$6:$AW$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$AX$6:$AX$500,('Master Schedule'!$AW$6:$AW$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$AY$6:$AY$500,('Master Schedule'!$AW$6:$AW$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$AZ$6:$AZ$500,('Master Schedule'!$AW$6:$AW$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;""))),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$AW$6:$AW$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$AW$6:$AW$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"No jobs in queue")</f>
+        <f>IFERROR(_xlfn._xlws.SEQUENCE(ROWS(_xlfn._xlws.FILTER('Master Schedule'!$A$6:$A$500,('Master Schedule'!$AW$6:$AW$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")))),"")</f>
+        <v/>
+      </c>
+      <c r="B8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$A$6:$A$500,('Master Schedule'!$AW$6:$AW$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$AW$6:$AW$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$AW$6:$AW$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"")</f>
+        <v/>
+      </c>
+      <c r="C8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$B$6:$B$500,('Master Schedule'!$AW$6:$AW$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$AW$6:$AW$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$AW$6:$AW$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"")</f>
+        <v/>
+      </c>
+      <c r="D8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$C$6:$C$500,('Master Schedule'!$AW$6:$AW$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$AW$6:$AW$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$AW$6:$AW$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"")</f>
+        <v/>
+      </c>
+      <c r="E8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$E$6:$E$500,('Master Schedule'!$AW$6:$AW$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$AW$6:$AW$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$AW$6:$AW$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"")</f>
+        <v/>
+      </c>
+      <c r="F8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$F$6:$F$500,('Master Schedule'!$AW$6:$AW$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$AW$6:$AW$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$AW$6:$AW$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"")</f>
+        <v/>
+      </c>
+      <c r="G8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$AW$6:$AW$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$AW$6:$AW$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$AW$6:$AW$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"")</f>
+        <v/>
+      </c>
+      <c r="H8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$J$6:$J$500,('Master Schedule'!$AW$6:$AW$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$AW$6:$AW$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$AW$6:$AW$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"")</f>
+        <v/>
+      </c>
+      <c r="I8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$AW$6:$AW$500,('Master Schedule'!$AW$6:$AW$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$AW$6:$AW$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$AW$6:$AW$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"")</f>
+        <v/>
+      </c>
+      <c r="J8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$AX$6:$AX$500,('Master Schedule'!$AW$6:$AW$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$AW$6:$AW$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$AW$6:$AW$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"")</f>
+        <v/>
+      </c>
+      <c r="K8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$AY$6:$AY$500,('Master Schedule'!$AW$6:$AW$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$AW$6:$AW$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$AW$6:$AW$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"")</f>
+        <v/>
+      </c>
+      <c r="L8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$AZ$6:$AZ$500,('Master Schedule'!$AW$6:$AW$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$AW$6:$AW$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$AW$6:$AW$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"")</f>
         <v/>
       </c>
     </row>
@@ -2094,7 +2314,51 @@
     </row>
     <row r="8">
       <c r="A8">
-        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn.HSTACK(_xlfn.SEQUENCE(ROWS(_xlfn._xlws.FILTER('Master Schedule'!$A$6:$A$500,('Master Schedule'!$BA$6:$BA$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")))),_xlfn._xlws.FILTER('Master Schedule'!$A$6:$A$500,('Master Schedule'!$BA$6:$BA$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$B$6:$B$500,('Master Schedule'!$BA$6:$BA$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$C$6:$C$500,('Master Schedule'!$BA$6:$BA$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$E$6:$E$500,('Master Schedule'!$BA$6:$BA$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$F$6:$F$500,('Master Schedule'!$BA$6:$BA$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$BA$6:$BA$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$J$6:$J$500,('Master Schedule'!$BA$6:$BA$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$BA$6:$BA$500,('Master Schedule'!$BA$6:$BA$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$BB$6:$BB$500,('Master Schedule'!$BA$6:$BA$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$BC$6:$BC$500,('Master Schedule'!$BA$6:$BA$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$BD$6:$BD$500,('Master Schedule'!$BA$6:$BA$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;""))),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$BA$6:$BA$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$BA$6:$BA$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"No jobs in queue")</f>
+        <f>IFERROR(_xlfn._xlws.SEQUENCE(ROWS(_xlfn._xlws.FILTER('Master Schedule'!$A$6:$A$500,('Master Schedule'!$BA$6:$BA$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")))),"")</f>
+        <v/>
+      </c>
+      <c r="B8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$A$6:$A$500,('Master Schedule'!$BA$6:$BA$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$BA$6:$BA$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$BA$6:$BA$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"")</f>
+        <v/>
+      </c>
+      <c r="C8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$B$6:$B$500,('Master Schedule'!$BA$6:$BA$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$BA$6:$BA$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$BA$6:$BA$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"")</f>
+        <v/>
+      </c>
+      <c r="D8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$C$6:$C$500,('Master Schedule'!$BA$6:$BA$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$BA$6:$BA$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$BA$6:$BA$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"")</f>
+        <v/>
+      </c>
+      <c r="E8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$E$6:$E$500,('Master Schedule'!$BA$6:$BA$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$BA$6:$BA$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$BA$6:$BA$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"")</f>
+        <v/>
+      </c>
+      <c r="F8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$F$6:$F$500,('Master Schedule'!$BA$6:$BA$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$BA$6:$BA$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$BA$6:$BA$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"")</f>
+        <v/>
+      </c>
+      <c r="G8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$BA$6:$BA$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$BA$6:$BA$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$BA$6:$BA$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"")</f>
+        <v/>
+      </c>
+      <c r="H8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$J$6:$J$500,('Master Schedule'!$BA$6:$BA$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$BA$6:$BA$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$BA$6:$BA$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"")</f>
+        <v/>
+      </c>
+      <c r="I8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$BA$6:$BA$500,('Master Schedule'!$BA$6:$BA$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$BA$6:$BA$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$BA$6:$BA$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"")</f>
+        <v/>
+      </c>
+      <c r="J8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$BB$6:$BB$500,('Master Schedule'!$BA$6:$BA$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$BA$6:$BA$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$BA$6:$BA$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"")</f>
+        <v/>
+      </c>
+      <c r="K8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$BC$6:$BC$500,('Master Schedule'!$BA$6:$BA$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$BA$6:$BA$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$BA$6:$BA$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"")</f>
+        <v/>
+      </c>
+      <c r="L8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$BD$6:$BD$500,('Master Schedule'!$BA$6:$BA$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$BA$6:$BA$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$BA$6:$BA$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"")</f>
         <v/>
       </c>
     </row>
@@ -2252,7 +2516,51 @@
     </row>
     <row r="8">
       <c r="A8">
-        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn.HSTACK(_xlfn.SEQUENCE(ROWS(_xlfn._xlws.FILTER('Master Schedule'!$A$6:$A$500,('Master Schedule'!$BE$6:$BE$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")))),_xlfn._xlws.FILTER('Master Schedule'!$A$6:$A$500,('Master Schedule'!$BE$6:$BE$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$B$6:$B$500,('Master Schedule'!$BE$6:$BE$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$C$6:$C$500,('Master Schedule'!$BE$6:$BE$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$E$6:$E$500,('Master Schedule'!$BE$6:$BE$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$F$6:$F$500,('Master Schedule'!$BE$6:$BE$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$BE$6:$BE$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$J$6:$J$500,('Master Schedule'!$BE$6:$BE$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$BE$6:$BE$500,('Master Schedule'!$BE$6:$BE$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$BF$6:$BF$500,('Master Schedule'!$BE$6:$BE$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$BG$6:$BG$500,('Master Schedule'!$BE$6:$BE$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$BH$6:$BH$500,('Master Schedule'!$BE$6:$BE$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;""))),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$BE$6:$BE$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$BE$6:$BE$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"No jobs in queue")</f>
+        <f>IFERROR(_xlfn._xlws.SEQUENCE(ROWS(_xlfn._xlws.FILTER('Master Schedule'!$A$6:$A$500,('Master Schedule'!$BE$6:$BE$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")))),"")</f>
+        <v/>
+      </c>
+      <c r="B8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$A$6:$A$500,('Master Schedule'!$BE$6:$BE$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$BE$6:$BE$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$BE$6:$BE$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"")</f>
+        <v/>
+      </c>
+      <c r="C8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$B$6:$B$500,('Master Schedule'!$BE$6:$BE$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$BE$6:$BE$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$BE$6:$BE$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"")</f>
+        <v/>
+      </c>
+      <c r="D8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$C$6:$C$500,('Master Schedule'!$BE$6:$BE$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$BE$6:$BE$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$BE$6:$BE$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"")</f>
+        <v/>
+      </c>
+      <c r="E8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$E$6:$E$500,('Master Schedule'!$BE$6:$BE$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$BE$6:$BE$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$BE$6:$BE$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"")</f>
+        <v/>
+      </c>
+      <c r="F8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$F$6:$F$500,('Master Schedule'!$BE$6:$BE$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$BE$6:$BE$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$BE$6:$BE$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"")</f>
+        <v/>
+      </c>
+      <c r="G8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$BE$6:$BE$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$BE$6:$BE$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$BE$6:$BE$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"")</f>
+        <v/>
+      </c>
+      <c r="H8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$J$6:$J$500,('Master Schedule'!$BE$6:$BE$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$BE$6:$BE$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$BE$6:$BE$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"")</f>
+        <v/>
+      </c>
+      <c r="I8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$BE$6:$BE$500,('Master Schedule'!$BE$6:$BE$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$BE$6:$BE$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$BE$6:$BE$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"")</f>
+        <v/>
+      </c>
+      <c r="J8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$BF$6:$BF$500,('Master Schedule'!$BE$6:$BE$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$BE$6:$BE$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$BE$6:$BE$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"")</f>
+        <v/>
+      </c>
+      <c r="K8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$BG$6:$BG$500,('Master Schedule'!$BE$6:$BE$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$BE$6:$BE$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$BE$6:$BE$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"")</f>
+        <v/>
+      </c>
+      <c r="L8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$BH$6:$BH$500,('Master Schedule'!$BE$6:$BE$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$BE$6:$BE$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$BE$6:$BE$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"")</f>
         <v/>
       </c>
     </row>
@@ -2410,7 +2718,51 @@
     </row>
     <row r="8">
       <c r="A8">
-        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn.HSTACK(_xlfn.SEQUENCE(ROWS(_xlfn._xlws.FILTER('Master Schedule'!$A$6:$A$500,('Master Schedule'!$BI$6:$BI$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")))),_xlfn._xlws.FILTER('Master Schedule'!$A$6:$A$500,('Master Schedule'!$BI$6:$BI$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$B$6:$B$500,('Master Schedule'!$BI$6:$BI$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$C$6:$C$500,('Master Schedule'!$BI$6:$BI$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$E$6:$E$500,('Master Schedule'!$BI$6:$BI$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$F$6:$F$500,('Master Schedule'!$BI$6:$BI$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$BI$6:$BI$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$J$6:$J$500,('Master Schedule'!$BI$6:$BI$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$BI$6:$BI$500,('Master Schedule'!$BI$6:$BI$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$BJ$6:$BJ$500,('Master Schedule'!$BI$6:$BI$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$BK$6:$BK$500,('Master Schedule'!$BI$6:$BI$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$BL$6:$BL$500,('Master Schedule'!$BI$6:$BI$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;""))),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$BI$6:$BI$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$BI$6:$BI$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"No jobs in queue")</f>
+        <f>IFERROR(_xlfn._xlws.SEQUENCE(ROWS(_xlfn._xlws.FILTER('Master Schedule'!$A$6:$A$500,('Master Schedule'!$BI$6:$BI$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")))),"")</f>
+        <v/>
+      </c>
+      <c r="B8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$A$6:$A$500,('Master Schedule'!$BI$6:$BI$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$BI$6:$BI$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$BI$6:$BI$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"")</f>
+        <v/>
+      </c>
+      <c r="C8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$B$6:$B$500,('Master Schedule'!$BI$6:$BI$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$BI$6:$BI$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$BI$6:$BI$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"")</f>
+        <v/>
+      </c>
+      <c r="D8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$C$6:$C$500,('Master Schedule'!$BI$6:$BI$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$BI$6:$BI$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$BI$6:$BI$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"")</f>
+        <v/>
+      </c>
+      <c r="E8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$E$6:$E$500,('Master Schedule'!$BI$6:$BI$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$BI$6:$BI$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$BI$6:$BI$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"")</f>
+        <v/>
+      </c>
+      <c r="F8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$F$6:$F$500,('Master Schedule'!$BI$6:$BI$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$BI$6:$BI$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$BI$6:$BI$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"")</f>
+        <v/>
+      </c>
+      <c r="G8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$BI$6:$BI$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$BI$6:$BI$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$BI$6:$BI$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"")</f>
+        <v/>
+      </c>
+      <c r="H8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$J$6:$J$500,('Master Schedule'!$BI$6:$BI$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$BI$6:$BI$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$BI$6:$BI$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"")</f>
+        <v/>
+      </c>
+      <c r="I8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$BI$6:$BI$500,('Master Schedule'!$BI$6:$BI$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$BI$6:$BI$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$BI$6:$BI$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"")</f>
+        <v/>
+      </c>
+      <c r="J8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$BJ$6:$BJ$500,('Master Schedule'!$BI$6:$BI$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$BI$6:$BI$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$BI$6:$BI$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"")</f>
+        <v/>
+      </c>
+      <c r="K8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$BK$6:$BK$500,('Master Schedule'!$BI$6:$BI$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$BI$6:$BI$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$BI$6:$BI$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"")</f>
+        <v/>
+      </c>
+      <c r="L8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$BL$6:$BL$500,('Master Schedule'!$BI$6:$BI$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$BI$6:$BI$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$BI$6:$BI$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"")</f>
         <v/>
       </c>
     </row>
@@ -8318,7 +8670,47 @@
     </row>
     <row r="8">
       <c r="A8">
-        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn.HSTACK(_xlfn.SEQUENCE(ROWS(_xlfn._xlws.FILTER('Master Schedule'!$A$6:$A$500,('Master Schedule'!$A$6:$A$500&lt;&gt;"")*IF($B$4="All",1,ISNUMBER(SEARCH($B$4,'Master Schedule'!$A$6:$A$500)))*IF($D$4="All",1,'Master Schedule'!$F$6:$F$500=$D$4)))),_xlfn._xlws.FILTER('Master Schedule'!$A$6:$A$500,('Master Schedule'!$A$6:$A$500&lt;&gt;"")*IF($D$4="All",1,'Master Schedule'!$F$6:$F$500=$D$4)),_xlfn._xlws.FILTER('Master Schedule'!$B$6:$B$500,('Master Schedule'!$A$6:$A$500&lt;&gt;"")*IF($D$4="All",1,'Master Schedule'!$F$6:$F$500=$D$4)),_xlfn._xlws.FILTER('Master Schedule'!$C$6:$C$500,('Master Schedule'!$A$6:$A$500&lt;&gt;"")*IF($D$4="All",1,'Master Schedule'!$F$6:$F$500=$D$4)),_xlfn._xlws.FILTER('Master Schedule'!$E$6:$E$500,('Master Schedule'!$A$6:$A$500&lt;&gt;"")*IF($D$4="All",1,'Master Schedule'!$F$6:$F$500=$D$4)),_xlfn._xlws.FILTER('Master Schedule'!$F$6:$F$500,('Master Schedule'!$A$6:$A$500&lt;&gt;"")*IF($D$4="All",1,'Master Schedule'!$F$6:$F$500=$D$4)),_xlfn._xlws.FILTER('Master Schedule'!$G$6:$G$500,('Master Schedule'!$A$6:$A$500&lt;&gt;"")*IF($D$4="All",1,'Master Schedule'!$F$6:$F$500=$D$4)),_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$A$6:$A$500&lt;&gt;"")*IF($D$4="All",1,'Master Schedule'!$F$6:$F$500=$D$4)),_xlfn._xlws.FILTER('Master Schedule'!$J$6:$J$500,('Master Schedule'!$A$6:$A$500&lt;&gt;"")*IF($D$4="All",1,'Master Schedule'!$F$6:$F$500=$D$4)),_xlfn._xlws.FILTER('Master Schedule'!$G$6:$G$500,('Master Schedule'!$A$6:$A$500&lt;&gt;"")*IF($D$4="All",1,'Master Schedule'!$F$6:$F$500=$D$4)),_xlfn._xlws.FILTER('Master Schedule'!$L$6:$L$500,('Master Schedule'!$A$6:$A$500&lt;&gt;"")*IF($D$4="All",1,'Master Schedule'!$F$6:$F$500=$D$4))),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$A$6:$A$500&lt;&gt;"")*IF($D$4="All",1,'Master Schedule'!$F$6:$F$500=$D$4)),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$A$6:$A$500&lt;&gt;"")*IF($D$4="All",1,'Master Schedule'!$F$6:$F$500=$D$4)),1),"No jobs match")</f>
+        <f>IFERROR(_xlfn._xlws.SEQUENCE(ROWS(_xlfn._xlws.FILTER('Master Schedule'!$A$6:$A$500,('Master Schedule'!$A$6:$A$500&lt;&gt;"")*IF($D$4="All",1,'Master Schedule'!$F$6:$F$500=$D$4)))),"")</f>
+        <v/>
+      </c>
+      <c r="B8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$A$6:$A$500,('Master Schedule'!$A$6:$A$500&lt;&gt;"")*IF($D$4="All",1,'Master Schedule'!$F$6:$F$500=$D$4)),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$A$6:$A$500&lt;&gt;"")*IF($D$4="All",1,'Master Schedule'!$F$6:$F$500=$D$4)),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$A$6:$A$500&lt;&gt;"")*IF($D$4="All",1,'Master Schedule'!$F$6:$F$500=$D$4)),1),"")</f>
+        <v/>
+      </c>
+      <c r="C8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$B$6:$B$500,('Master Schedule'!$A$6:$A$500&lt;&gt;"")*IF($D$4="All",1,'Master Schedule'!$F$6:$F$500=$D$4)),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$A$6:$A$500&lt;&gt;"")*IF($D$4="All",1,'Master Schedule'!$F$6:$F$500=$D$4)),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$A$6:$A$500&lt;&gt;"")*IF($D$4="All",1,'Master Schedule'!$F$6:$F$500=$D$4)),1),"")</f>
+        <v/>
+      </c>
+      <c r="D8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$C$6:$C$500,('Master Schedule'!$A$6:$A$500&lt;&gt;"")*IF($D$4="All",1,'Master Schedule'!$F$6:$F$500=$D$4)),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$A$6:$A$500&lt;&gt;"")*IF($D$4="All",1,'Master Schedule'!$F$6:$F$500=$D$4)),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$A$6:$A$500&lt;&gt;"")*IF($D$4="All",1,'Master Schedule'!$F$6:$F$500=$D$4)),1),"")</f>
+        <v/>
+      </c>
+      <c r="E8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$E$6:$E$500,('Master Schedule'!$A$6:$A$500&lt;&gt;"")*IF($D$4="All",1,'Master Schedule'!$F$6:$F$500=$D$4)),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$A$6:$A$500&lt;&gt;"")*IF($D$4="All",1,'Master Schedule'!$F$6:$F$500=$D$4)),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$A$6:$A$500&lt;&gt;"")*IF($D$4="All",1,'Master Schedule'!$F$6:$F$500=$D$4)),1),"")</f>
+        <v/>
+      </c>
+      <c r="F8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$F$6:$F$500,('Master Schedule'!$A$6:$A$500&lt;&gt;"")*IF($D$4="All",1,'Master Schedule'!$F$6:$F$500=$D$4)),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$A$6:$A$500&lt;&gt;"")*IF($D$4="All",1,'Master Schedule'!$F$6:$F$500=$D$4)),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$A$6:$A$500&lt;&gt;"")*IF($D$4="All",1,'Master Schedule'!$F$6:$F$500=$D$4)),1),"")</f>
+        <v/>
+      </c>
+      <c r="G8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$G$6:$G$500,('Master Schedule'!$A$6:$A$500&lt;&gt;"")*IF($D$4="All",1,'Master Schedule'!$F$6:$F$500=$D$4)),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$A$6:$A$500&lt;&gt;"")*IF($D$4="All",1,'Master Schedule'!$F$6:$F$500=$D$4)),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$A$6:$A$500&lt;&gt;"")*IF($D$4="All",1,'Master Schedule'!$F$6:$F$500=$D$4)),1),"")</f>
+        <v/>
+      </c>
+      <c r="H8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$A$6:$A$500&lt;&gt;"")*IF($D$4="All",1,'Master Schedule'!$F$6:$F$500=$D$4)),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$A$6:$A$500&lt;&gt;"")*IF($D$4="All",1,'Master Schedule'!$F$6:$F$500=$D$4)),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$A$6:$A$500&lt;&gt;"")*IF($D$4="All",1,'Master Schedule'!$F$6:$F$500=$D$4)),1),"")</f>
+        <v/>
+      </c>
+      <c r="I8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$J$6:$J$500,('Master Schedule'!$A$6:$A$500&lt;&gt;"")*IF($D$4="All",1,'Master Schedule'!$F$6:$F$500=$D$4)),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$A$6:$A$500&lt;&gt;"")*IF($D$4="All",1,'Master Schedule'!$F$6:$F$500=$D$4)),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$A$6:$A$500&lt;&gt;"")*IF($D$4="All",1,'Master Schedule'!$F$6:$F$500=$D$4)),1),"")</f>
+        <v/>
+      </c>
+      <c r="J8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$G$6:$G$500,('Master Schedule'!$A$6:$A$500&lt;&gt;"")*IF($D$4="All",1,'Master Schedule'!$F$6:$F$500=$D$4)),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$A$6:$A$500&lt;&gt;"")*IF($D$4="All",1,'Master Schedule'!$F$6:$F$500=$D$4)),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$A$6:$A$500&lt;&gt;"")*IF($D$4="All",1,'Master Schedule'!$F$6:$F$500=$D$4)),1),"")</f>
+        <v/>
+      </c>
+      <c r="K8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$L$6:$L$500,('Master Schedule'!$A$6:$A$500&lt;&gt;"")*IF($D$4="All",1,'Master Schedule'!$F$6:$F$500=$D$4)),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$A$6:$A$500&lt;&gt;"")*IF($D$4="All",1,'Master Schedule'!$F$6:$F$500=$D$4)),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$A$6:$A$500&lt;&gt;"")*IF($D$4="All",1,'Master Schedule'!$F$6:$F$500=$D$4)),1),"")</f>
         <v/>
       </c>
     </row>
@@ -8477,7 +8869,51 @@
     </row>
     <row r="8">
       <c r="A8">
-        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn.HSTACK(_xlfn.SEQUENCE(ROWS(_xlfn._xlws.FILTER('Master Schedule'!$A$6:$A$500,('Master Schedule'!$M$6:$M$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")))),_xlfn._xlws.FILTER('Master Schedule'!$A$6:$A$500,('Master Schedule'!$M$6:$M$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$B$6:$B$500,('Master Schedule'!$M$6:$M$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$C$6:$C$500,('Master Schedule'!$M$6:$M$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$E$6:$E$500,('Master Schedule'!$M$6:$M$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$F$6:$F$500,('Master Schedule'!$M$6:$M$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$M$6:$M$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$J$6:$J$500,('Master Schedule'!$M$6:$M$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$M$6:$M$500,('Master Schedule'!$M$6:$M$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$N$6:$N$500,('Master Schedule'!$M$6:$M$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$O$6:$O$500,('Master Schedule'!$M$6:$M$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$P$6:$P$500,('Master Schedule'!$M$6:$M$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;""))),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$M$6:$M$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$M$6:$M$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"No jobs in queue")</f>
+        <f>IFERROR(_xlfn._xlws.SEQUENCE(ROWS(_xlfn._xlws.FILTER('Master Schedule'!$A$6:$A$500,('Master Schedule'!$M$6:$M$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")))),"")</f>
+        <v/>
+      </c>
+      <c r="B8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$A$6:$A$500,('Master Schedule'!$M$6:$M$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$M$6:$M$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$M$6:$M$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"")</f>
+        <v/>
+      </c>
+      <c r="C8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$B$6:$B$500,('Master Schedule'!$M$6:$M$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$M$6:$M$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$M$6:$M$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"")</f>
+        <v/>
+      </c>
+      <c r="D8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$C$6:$C$500,('Master Schedule'!$M$6:$M$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$M$6:$M$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$M$6:$M$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"")</f>
+        <v/>
+      </c>
+      <c r="E8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$E$6:$E$500,('Master Schedule'!$M$6:$M$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$M$6:$M$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$M$6:$M$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"")</f>
+        <v/>
+      </c>
+      <c r="F8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$F$6:$F$500,('Master Schedule'!$M$6:$M$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$M$6:$M$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$M$6:$M$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"")</f>
+        <v/>
+      </c>
+      <c r="G8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$M$6:$M$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$M$6:$M$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$M$6:$M$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"")</f>
+        <v/>
+      </c>
+      <c r="H8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$J$6:$J$500,('Master Schedule'!$M$6:$M$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$M$6:$M$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$M$6:$M$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"")</f>
+        <v/>
+      </c>
+      <c r="I8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$M$6:$M$500,('Master Schedule'!$M$6:$M$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$M$6:$M$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$M$6:$M$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"")</f>
+        <v/>
+      </c>
+      <c r="J8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$N$6:$N$500,('Master Schedule'!$M$6:$M$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$M$6:$M$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$M$6:$M$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"")</f>
+        <v/>
+      </c>
+      <c r="K8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$O$6:$O$500,('Master Schedule'!$M$6:$M$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$M$6:$M$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$M$6:$M$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"")</f>
+        <v/>
+      </c>
+      <c r="L8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$P$6:$P$500,('Master Schedule'!$M$6:$M$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$M$6:$M$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$M$6:$M$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"")</f>
         <v/>
       </c>
     </row>
@@ -8635,7 +9071,51 @@
     </row>
     <row r="8">
       <c r="A8">
-        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn.HSTACK(_xlfn.SEQUENCE(ROWS(_xlfn._xlws.FILTER('Master Schedule'!$A$6:$A$500,('Master Schedule'!$Q$6:$Q$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")))),_xlfn._xlws.FILTER('Master Schedule'!$A$6:$A$500,('Master Schedule'!$Q$6:$Q$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$B$6:$B$500,('Master Schedule'!$Q$6:$Q$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$C$6:$C$500,('Master Schedule'!$Q$6:$Q$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$E$6:$E$500,('Master Schedule'!$Q$6:$Q$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$F$6:$F$500,('Master Schedule'!$Q$6:$Q$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$Q$6:$Q$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$J$6:$J$500,('Master Schedule'!$Q$6:$Q$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$Q$6:$Q$500,('Master Schedule'!$Q$6:$Q$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$R$6:$R$500,('Master Schedule'!$Q$6:$Q$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$S$6:$S$500,('Master Schedule'!$Q$6:$Q$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$T$6:$T$500,('Master Schedule'!$Q$6:$Q$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;""))),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$Q$6:$Q$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$Q$6:$Q$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"No jobs in queue")</f>
+        <f>IFERROR(_xlfn._xlws.SEQUENCE(ROWS(_xlfn._xlws.FILTER('Master Schedule'!$A$6:$A$500,('Master Schedule'!$Q$6:$Q$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")))),"")</f>
+        <v/>
+      </c>
+      <c r="B8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$A$6:$A$500,('Master Schedule'!$Q$6:$Q$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$Q$6:$Q$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$Q$6:$Q$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"")</f>
+        <v/>
+      </c>
+      <c r="C8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$B$6:$B$500,('Master Schedule'!$Q$6:$Q$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$Q$6:$Q$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$Q$6:$Q$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"")</f>
+        <v/>
+      </c>
+      <c r="D8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$C$6:$C$500,('Master Schedule'!$Q$6:$Q$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$Q$6:$Q$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$Q$6:$Q$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"")</f>
+        <v/>
+      </c>
+      <c r="E8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$E$6:$E$500,('Master Schedule'!$Q$6:$Q$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$Q$6:$Q$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$Q$6:$Q$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"")</f>
+        <v/>
+      </c>
+      <c r="F8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$F$6:$F$500,('Master Schedule'!$Q$6:$Q$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$Q$6:$Q$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$Q$6:$Q$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"")</f>
+        <v/>
+      </c>
+      <c r="G8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$Q$6:$Q$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$Q$6:$Q$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$Q$6:$Q$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"")</f>
+        <v/>
+      </c>
+      <c r="H8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$J$6:$J$500,('Master Schedule'!$Q$6:$Q$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$Q$6:$Q$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$Q$6:$Q$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"")</f>
+        <v/>
+      </c>
+      <c r="I8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$Q$6:$Q$500,('Master Schedule'!$Q$6:$Q$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$Q$6:$Q$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$Q$6:$Q$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"")</f>
+        <v/>
+      </c>
+      <c r="J8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$R$6:$R$500,('Master Schedule'!$Q$6:$Q$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$Q$6:$Q$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$Q$6:$Q$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"")</f>
+        <v/>
+      </c>
+      <c r="K8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$S$6:$S$500,('Master Schedule'!$Q$6:$Q$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$Q$6:$Q$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$Q$6:$Q$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"")</f>
+        <v/>
+      </c>
+      <c r="L8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$T$6:$T$500,('Master Schedule'!$Q$6:$Q$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$Q$6:$Q$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$Q$6:$Q$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"")</f>
         <v/>
       </c>
     </row>
@@ -8793,7 +9273,51 @@
     </row>
     <row r="8">
       <c r="A8">
-        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn.HSTACK(_xlfn.SEQUENCE(ROWS(_xlfn._xlws.FILTER('Master Schedule'!$A$6:$A$500,('Master Schedule'!$U$6:$U$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")))),_xlfn._xlws.FILTER('Master Schedule'!$A$6:$A$500,('Master Schedule'!$U$6:$U$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$B$6:$B$500,('Master Schedule'!$U$6:$U$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$C$6:$C$500,('Master Schedule'!$U$6:$U$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$E$6:$E$500,('Master Schedule'!$U$6:$U$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$F$6:$F$500,('Master Schedule'!$U$6:$U$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$U$6:$U$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$J$6:$J$500,('Master Schedule'!$U$6:$U$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$U$6:$U$500,('Master Schedule'!$U$6:$U$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$V$6:$V$500,('Master Schedule'!$U$6:$U$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$W$6:$W$500,('Master Schedule'!$U$6:$U$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$X$6:$X$500,('Master Schedule'!$U$6:$U$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;""))),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$U$6:$U$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$U$6:$U$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"No jobs in queue")</f>
+        <f>IFERROR(_xlfn._xlws.SEQUENCE(ROWS(_xlfn._xlws.FILTER('Master Schedule'!$A$6:$A$500,('Master Schedule'!$U$6:$U$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")))),"")</f>
+        <v/>
+      </c>
+      <c r="B8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$A$6:$A$500,('Master Schedule'!$U$6:$U$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$U$6:$U$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$U$6:$U$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"")</f>
+        <v/>
+      </c>
+      <c r="C8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$B$6:$B$500,('Master Schedule'!$U$6:$U$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$U$6:$U$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$U$6:$U$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"")</f>
+        <v/>
+      </c>
+      <c r="D8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$C$6:$C$500,('Master Schedule'!$U$6:$U$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$U$6:$U$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$U$6:$U$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"")</f>
+        <v/>
+      </c>
+      <c r="E8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$E$6:$E$500,('Master Schedule'!$U$6:$U$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$U$6:$U$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$U$6:$U$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"")</f>
+        <v/>
+      </c>
+      <c r="F8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$F$6:$F$500,('Master Schedule'!$U$6:$U$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$U$6:$U$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$U$6:$U$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"")</f>
+        <v/>
+      </c>
+      <c r="G8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$U$6:$U$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$U$6:$U$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$U$6:$U$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"")</f>
+        <v/>
+      </c>
+      <c r="H8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$J$6:$J$500,('Master Schedule'!$U$6:$U$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$U$6:$U$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$U$6:$U$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"")</f>
+        <v/>
+      </c>
+      <c r="I8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$U$6:$U$500,('Master Schedule'!$U$6:$U$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$U$6:$U$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$U$6:$U$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"")</f>
+        <v/>
+      </c>
+      <c r="J8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$V$6:$V$500,('Master Schedule'!$U$6:$U$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$U$6:$U$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$U$6:$U$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"")</f>
+        <v/>
+      </c>
+      <c r="K8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$W$6:$W$500,('Master Schedule'!$U$6:$U$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$U$6:$U$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$U$6:$U$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"")</f>
+        <v/>
+      </c>
+      <c r="L8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$X$6:$X$500,('Master Schedule'!$U$6:$U$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$U$6:$U$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$U$6:$U$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"")</f>
         <v/>
       </c>
     </row>
@@ -8951,7 +9475,51 @@
     </row>
     <row r="8">
       <c r="A8">
-        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn.HSTACK(_xlfn.SEQUENCE(ROWS(_xlfn._xlws.FILTER('Master Schedule'!$A$6:$A$500,('Master Schedule'!$Y$6:$Y$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")))),_xlfn._xlws.FILTER('Master Schedule'!$A$6:$A$500,('Master Schedule'!$Y$6:$Y$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$B$6:$B$500,('Master Schedule'!$Y$6:$Y$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$C$6:$C$500,('Master Schedule'!$Y$6:$Y$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$E$6:$E$500,('Master Schedule'!$Y$6:$Y$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$F$6:$F$500,('Master Schedule'!$Y$6:$Y$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$Y$6:$Y$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$J$6:$J$500,('Master Schedule'!$Y$6:$Y$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$Y$6:$Y$500,('Master Schedule'!$Y$6:$Y$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$Z$6:$Z$500,('Master Schedule'!$Y$6:$Y$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$AA$6:$AA$500,('Master Schedule'!$Y$6:$Y$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$AB$6:$AB$500,('Master Schedule'!$Y$6:$Y$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;""))),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$Y$6:$Y$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$Y$6:$Y$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"No jobs in queue")</f>
+        <f>IFERROR(_xlfn._xlws.SEQUENCE(ROWS(_xlfn._xlws.FILTER('Master Schedule'!$A$6:$A$500,('Master Schedule'!$Y$6:$Y$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")))),"")</f>
+        <v/>
+      </c>
+      <c r="B8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$A$6:$A$500,('Master Schedule'!$Y$6:$Y$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$Y$6:$Y$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$Y$6:$Y$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"")</f>
+        <v/>
+      </c>
+      <c r="C8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$B$6:$B$500,('Master Schedule'!$Y$6:$Y$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$Y$6:$Y$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$Y$6:$Y$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"")</f>
+        <v/>
+      </c>
+      <c r="D8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$C$6:$C$500,('Master Schedule'!$Y$6:$Y$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$Y$6:$Y$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$Y$6:$Y$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"")</f>
+        <v/>
+      </c>
+      <c r="E8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$E$6:$E$500,('Master Schedule'!$Y$6:$Y$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$Y$6:$Y$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$Y$6:$Y$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"")</f>
+        <v/>
+      </c>
+      <c r="F8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$F$6:$F$500,('Master Schedule'!$Y$6:$Y$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$Y$6:$Y$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$Y$6:$Y$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"")</f>
+        <v/>
+      </c>
+      <c r="G8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$Y$6:$Y$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$Y$6:$Y$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$Y$6:$Y$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"")</f>
+        <v/>
+      </c>
+      <c r="H8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$J$6:$J$500,('Master Schedule'!$Y$6:$Y$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$Y$6:$Y$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$Y$6:$Y$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"")</f>
+        <v/>
+      </c>
+      <c r="I8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$Y$6:$Y$500,('Master Schedule'!$Y$6:$Y$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$Y$6:$Y$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$Y$6:$Y$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"")</f>
+        <v/>
+      </c>
+      <c r="J8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$Z$6:$Z$500,('Master Schedule'!$Y$6:$Y$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$Y$6:$Y$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$Y$6:$Y$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"")</f>
+        <v/>
+      </c>
+      <c r="K8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$AA$6:$AA$500,('Master Schedule'!$Y$6:$Y$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$Y$6:$Y$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$Y$6:$Y$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"")</f>
+        <v/>
+      </c>
+      <c r="L8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$AB$6:$AB$500,('Master Schedule'!$Y$6:$Y$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$Y$6:$Y$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$Y$6:$Y$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"")</f>
         <v/>
       </c>
     </row>
@@ -9109,7 +9677,51 @@
     </row>
     <row r="8">
       <c r="A8">
-        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn.HSTACK(_xlfn.SEQUENCE(ROWS(_xlfn._xlws.FILTER('Master Schedule'!$A$6:$A$500,('Master Schedule'!$AC$6:$AC$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")))),_xlfn._xlws.FILTER('Master Schedule'!$A$6:$A$500,('Master Schedule'!$AC$6:$AC$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$B$6:$B$500,('Master Schedule'!$AC$6:$AC$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$C$6:$C$500,('Master Schedule'!$AC$6:$AC$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$E$6:$E$500,('Master Schedule'!$AC$6:$AC$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$F$6:$F$500,('Master Schedule'!$AC$6:$AC$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$AC$6:$AC$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$J$6:$J$500,('Master Schedule'!$AC$6:$AC$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$AC$6:$AC$500,('Master Schedule'!$AC$6:$AC$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$AD$6:$AD$500,('Master Schedule'!$AC$6:$AC$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$AE$6:$AE$500,('Master Schedule'!$AC$6:$AC$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$AF$6:$AF$500,('Master Schedule'!$AC$6:$AC$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;""))),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$AC$6:$AC$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$AC$6:$AC$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"No jobs in queue")</f>
+        <f>IFERROR(_xlfn._xlws.SEQUENCE(ROWS(_xlfn._xlws.FILTER('Master Schedule'!$A$6:$A$500,('Master Schedule'!$AC$6:$AC$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")))),"")</f>
+        <v/>
+      </c>
+      <c r="B8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$A$6:$A$500,('Master Schedule'!$AC$6:$AC$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$AC$6:$AC$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$AC$6:$AC$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"")</f>
+        <v/>
+      </c>
+      <c r="C8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$B$6:$B$500,('Master Schedule'!$AC$6:$AC$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$AC$6:$AC$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$AC$6:$AC$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"")</f>
+        <v/>
+      </c>
+      <c r="D8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$C$6:$C$500,('Master Schedule'!$AC$6:$AC$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$AC$6:$AC$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$AC$6:$AC$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"")</f>
+        <v/>
+      </c>
+      <c r="E8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$E$6:$E$500,('Master Schedule'!$AC$6:$AC$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$AC$6:$AC$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$AC$6:$AC$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"")</f>
+        <v/>
+      </c>
+      <c r="F8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$F$6:$F$500,('Master Schedule'!$AC$6:$AC$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$AC$6:$AC$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$AC$6:$AC$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"")</f>
+        <v/>
+      </c>
+      <c r="G8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$AC$6:$AC$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$AC$6:$AC$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$AC$6:$AC$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"")</f>
+        <v/>
+      </c>
+      <c r="H8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$J$6:$J$500,('Master Schedule'!$AC$6:$AC$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$AC$6:$AC$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$AC$6:$AC$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"")</f>
+        <v/>
+      </c>
+      <c r="I8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$AC$6:$AC$500,('Master Schedule'!$AC$6:$AC$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$AC$6:$AC$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$AC$6:$AC$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"")</f>
+        <v/>
+      </c>
+      <c r="J8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$AD$6:$AD$500,('Master Schedule'!$AC$6:$AC$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$AC$6:$AC$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$AC$6:$AC$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"")</f>
+        <v/>
+      </c>
+      <c r="K8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$AE$6:$AE$500,('Master Schedule'!$AC$6:$AC$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$AC$6:$AC$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$AC$6:$AC$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"")</f>
+        <v/>
+      </c>
+      <c r="L8">
+        <f>IFERROR(_xlfn._xlws.SORTBY(_xlfn._xlws.FILTER('Master Schedule'!$AF$6:$AF$500,('Master Schedule'!$AC$6:$AC$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),_xlfn._xlws.FILTER('Master Schedule'!$K$6:$K$500,('Master Schedule'!$AC$6:$AC$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1,_xlfn._xlws.FILTER('Master Schedule'!$H$6:$H$500,('Master Schedule'!$AC$6:$AC$500&lt;&gt;"Not Started")*('Master Schedule'!$A$6:$A$500&lt;&gt;"")),1),"")</f>
         <v/>
       </c>
     </row>
